--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_equip_regenerationCost.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_equip_regenerationCost.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="cfg_equip_regenerationCost" sheetId="1" r:id="rId1"/>
@@ -1210,10 +1210,10 @@
         <v>1</v>
       </c>
       <c r="E5" s="6">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F5" s="6">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>22</v>
@@ -1233,10 +1233,10 @@
         <v>2</v>
       </c>
       <c r="E6" s="6">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F6" s="6">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>22</v>
@@ -1256,10 +1256,10 @@
         <v>3</v>
       </c>
       <c r="E7" s="6">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F7" s="6">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>22</v>
@@ -1279,10 +1279,10 @@
         <v>4</v>
       </c>
       <c r="E8" s="6">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F8" s="6">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>22</v>
@@ -1348,10 +1348,10 @@
         <v>1</v>
       </c>
       <c r="E11" s="6">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F11" s="6">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="G11" s="6" t="s">
         <v>22</v>
@@ -1371,10 +1371,10 @@
         <v>2</v>
       </c>
       <c r="E12" s="6">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F12" s="6">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="G12" s="6" t="s">
         <v>22</v>
@@ -1394,10 +1394,10 @@
         <v>3</v>
       </c>
       <c r="E13" s="6">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F13" s="6">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>22</v>
@@ -1417,10 +1417,10 @@
         <v>4</v>
       </c>
       <c r="E14" s="6">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="F14" s="6">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="G14" s="6" t="s">
         <v>22</v>
